--- a/pdf/RTTBC26-Schedule-by-Division.xlsx
+++ b/pdf/RTTBC26-Schedule-by-Division.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/299f8723705ec823/Webmaster/gallop-racing/pdf/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1310" documentId="8_{DAECCBE5-FF72-4188-B2F1-1541968A3FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A213F005-6B83-4C67-8B46-2D32B9DCC126}"/>
+  <xr:revisionPtr revIDLastSave="1608" documentId="8_{DAECCBE5-FF72-4188-B2F1-1541968A3FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2412A872-B8A8-4258-A052-180374A1C0D7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{EAD27B02-19FE-4D48-9014-ED6E24DB84F0}"/>
   </bookViews>
@@ -338,9 +338,6 @@
     <t>Chicago H.-G2</t>
   </si>
   <si>
-    <t>Kelly's Landing S.-G3</t>
-  </si>
-  <si>
     <t>Summertime Oaks.-G3</t>
   </si>
   <si>
@@ -375,13 +372,16 @@
   </si>
   <si>
     <t>Hanshin S.-G3</t>
+  </si>
+  <si>
+    <t>Bango S.-G3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,6 +512,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -539,7 +545,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -689,11 +695,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -701,9 +734,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -729,9 +759,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -763,17 +790,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -785,9 +803,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -795,18 +810,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -836,32 +839,142 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -870,12 +983,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -888,43 +995,31 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -939,22 +1034,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -963,6 +1073,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -989,12 +1117,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1319,871 +1447,867 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1783450-6415-4D0D-A0B8-DEE615502A89}">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="4.28515625" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="32.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="32.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.7109375" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="92"/>
-      <c r="B1" s="92"/>
-      <c r="C1" s="101" t="s">
+      <c r="A1" s="117"/>
+      <c r="B1" s="117"/>
+      <c r="C1" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
     </row>
     <row r="2" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="133" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="29" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="24" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="103"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="30" t="s">
+      <c r="A3" s="133"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="30" t="s">
+      <c r="I3" s="25" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="103"/>
-      <c r="B4" s="78">
+      <c r="A4" s="133"/>
+      <c r="B4" s="118">
         <v>1</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="58" t="s">
+      <c r="E4" s="76"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="133"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="64" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A5" s="103"/>
-      <c r="B5" s="79"/>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="133"/>
+      <c r="B6" s="78">
+        <v>2</v>
+      </c>
+      <c r="C6" s="76"/>
+      <c r="D6" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="80"/>
+      <c r="I6" s="76"/>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="133"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="77"/>
+      <c r="D7" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="75"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="77"/>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="133"/>
+      <c r="B8" s="63">
+        <v>3</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="133"/>
+      <c r="B9" s="118">
+        <v>4</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="76"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="90"/>
+      <c r="I9" s="74" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="35" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="133"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="89"/>
+      <c r="G10" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="91"/>
+      <c r="I10" s="75"/>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="133"/>
+      <c r="B11" s="56">
+        <v>5</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="E11" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="61" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="37"/>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="133"/>
+      <c r="B12" s="78">
+        <v>6</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="I12" s="76"/>
+    </row>
+    <row r="13" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="133"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="75"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="77"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="133"/>
+      <c r="B14" s="118">
+        <v>7</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="84" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="76"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+    </row>
+    <row r="15" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="133"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="85"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="85"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="133"/>
+      <c r="B16" s="118">
+        <v>8</v>
+      </c>
+      <c r="C16" s="106"/>
+      <c r="D16" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="120"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="106" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A17" s="133"/>
+      <c r="B17" s="123"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="121"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="133"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="122"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="70"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="47"/>
+    </row>
+    <row r="19" spans="1:9" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="133"/>
+      <c r="B19" s="56">
+        <v>9</v>
+      </c>
+      <c r="C19" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A20" s="133"/>
+      <c r="B20" s="78">
         <v>10</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="C20" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="76"/>
+      <c r="E20" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="74" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="76"/>
+      <c r="H20" s="97" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" s="76"/>
+    </row>
+    <row r="21" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="133"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="77"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="77"/>
+    </row>
+    <row r="22" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="133"/>
+      <c r="B22" s="56">
+        <v>11</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="133"/>
+      <c r="B23" s="62">
+        <v>12</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="46"/>
+    </row>
+    <row r="24" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A24" s="133"/>
+      <c r="B24" s="78">
+        <v>13</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="97"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I24" s="76"/>
+    </row>
+    <row r="25" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A25" s="133"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="116"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" s="92"/>
+    </row>
+    <row r="26" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="133"/>
+      <c r="B26" s="79"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="42"/>
+      <c r="I26" s="77"/>
+    </row>
+    <row r="27" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="A27" s="133"/>
+      <c r="B27" s="78">
+        <v>14</v>
+      </c>
+      <c r="C27" s="93"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="93"/>
+      <c r="H27" s="95" t="s">
+        <v>96</v>
+      </c>
+      <c r="I27" s="76"/>
+    </row>
+    <row r="28" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="133"/>
+      <c r="B28" s="79"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="G28" s="94"/>
+      <c r="H28" s="96"/>
+      <c r="I28" s="77"/>
+    </row>
+    <row r="29" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="133"/>
+      <c r="B29" s="66">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="F29" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="68" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="133"/>
+      <c r="B30" s="78">
+        <v>16</v>
+      </c>
+      <c r="C30" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="97" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="114"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="84" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="133"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="98"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="85"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="133"/>
+      <c r="B32" s="118">
+        <v>17</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="E32" s="76"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="130" t="s">
+        <v>69</v>
+      </c>
+      <c r="H32" s="84" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A33" s="133"/>
+      <c r="B33" s="123"/>
+      <c r="C33" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="103"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="7" t="s">
+      <c r="D33" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="21"/>
-    </row>
-    <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="103"/>
-      <c r="B7" s="33">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="103"/>
-      <c r="B8" s="33">
-        <v>3</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="103"/>
-      <c r="B9" s="78">
-        <v>4</v>
-      </c>
-      <c r="C9" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="62"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H9" s="66"/>
-      <c r="I9" s="56" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="45" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="103"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="59"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="54" t="s">
-        <v>112</v>
-      </c>
-      <c r="H10" s="67"/>
-      <c r="I10" s="57"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="103"/>
-      <c r="B11" s="78">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="56" t="s">
+      <c r="E33" s="92"/>
+      <c r="F33" s="92"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="110"/>
+      <c r="I33" s="41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="133"/>
+      <c r="B34" s="123"/>
+      <c r="C34" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="134" t="s">
+        <v>75</v>
+      </c>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="110"/>
+      <c r="I34" s="104"/>
+    </row>
+    <row r="35" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="133"/>
+      <c r="B35" s="123"/>
+      <c r="C35" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="134"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="131"/>
+      <c r="H35" s="110"/>
+      <c r="I35" s="104"/>
+    </row>
+    <row r="36" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A36" s="133"/>
+      <c r="B36" s="78">
+        <v>18</v>
+      </c>
+      <c r="C36" s="101"/>
+      <c r="D36" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="G36" s="76"/>
+      <c r="H36" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="I36" s="86" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="21" x14ac:dyDescent="0.35">
+      <c r="A37" s="133"/>
+      <c r="B37" s="100"/>
+      <c r="C37" s="102"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="G37" s="92"/>
+      <c r="H37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I37" s="105"/>
+    </row>
+    <row r="38" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="133"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" s="77"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="87"/>
+    </row>
+    <row r="39" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="133"/>
+      <c r="B39" s="63">
         <v>20</v>
       </c>
-      <c r="E11" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="56"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="103"/>
-      <c r="B12" s="79"/>
-      <c r="C12" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="75"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="75"/>
-    </row>
-    <row r="13" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="103"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="7" t="s">
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="117"/>
+      <c r="B40" s="99" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="99"/>
+      <c r="D40" s="99"/>
+      <c r="E40" s="99"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="99"/>
+      <c r="H40" s="99"/>
+      <c r="I40" s="129"/>
+    </row>
+    <row r="41" spans="1:9" s="14" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="117"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="15">
+        <f>COUNTIF(C4:C39, "&lt;&gt;")</f>
         <v>21</v>
       </c>
-      <c r="D13" s="75"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="37"/>
-      <c r="I13" s="75"/>
-    </row>
-    <row r="14" spans="1:9" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="103"/>
-      <c r="B14" s="33">
-        <v>6</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A15" s="103"/>
-      <c r="B15" s="78">
-        <v>7</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="68" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="68" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A16" s="103"/>
-      <c r="B16" s="79"/>
-      <c r="C16" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="69"/>
-    </row>
-    <row r="17" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="103"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="63"/>
-      <c r="F17" s="63"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="76"/>
-      <c r="I17" s="76"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="103"/>
-      <c r="B18" s="78">
-        <v>8</v>
-      </c>
-      <c r="C18" s="68" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="87" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="62"/>
-      <c r="I18" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="103"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="76"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="22" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A20" s="103"/>
-      <c r="B20" s="78">
+      <c r="D41" s="15">
+        <f>COUNTIF(D4:D39, "&lt;&gt;")</f>
+        <v>20</v>
+      </c>
+      <c r="E41" s="15">
+        <f t="shared" ref="E41:I41" si="0">COUNTIF(E4:E39, "&lt;&gt;")</f>
         <v>9</v>
       </c>
-      <c r="C20" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="68" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="56" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="62"/>
-      <c r="H20" s="89" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" s="62"/>
-    </row>
-    <row r="21" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="103"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="69"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="91"/>
-      <c r="I21" s="71"/>
-    </row>
-    <row r="22" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="103"/>
-      <c r="B22" s="38">
-        <v>10</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="103"/>
-      <c r="B23" s="38">
-        <v>11</v>
-      </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A24" s="103"/>
-      <c r="B24" s="78">
-        <v>12</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="62"/>
-    </row>
-    <row r="25" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A25" s="103"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I25" s="71"/>
-    </row>
-    <row r="26" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="103"/>
-      <c r="B26" s="80"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="I26" s="63"/>
-    </row>
-    <row r="27" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A27" s="103"/>
-      <c r="B27" s="78">
-        <v>13</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="E27" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="56" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" s="62"/>
-    </row>
-    <row r="28" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="103"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="57"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="59"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="63"/>
-    </row>
-    <row r="29" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="103"/>
-      <c r="B29" s="33">
-        <v>14</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-    </row>
-    <row r="30" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="103"/>
-      <c r="B30" s="33">
-        <v>15</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-    </row>
-    <row r="31" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="103"/>
-      <c r="B31" s="78">
-        <v>16</v>
-      </c>
-      <c r="C31" s="89" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="89" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="72"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="I31" s="68" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="103"/>
-      <c r="B32" s="79"/>
-      <c r="C32" s="90"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="I32" s="69"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="103"/>
-      <c r="B33" s="78">
-        <v>17</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="99" t="s">
-        <v>69</v>
-      </c>
-      <c r="H33" s="68" t="s">
-        <v>65</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A34" s="103"/>
-      <c r="B34" s="79"/>
-      <c r="C34" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="100"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="103"/>
-      <c r="B35" s="79"/>
-      <c r="C35" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="102" t="s">
-        <v>75</v>
-      </c>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="100"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="84"/>
-    </row>
-    <row r="36" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="103"/>
-      <c r="B36" s="79"/>
-      <c r="C36" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="88"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="85"/>
-    </row>
-    <row r="37" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="103"/>
-      <c r="B37" s="78">
-        <v>18</v>
-      </c>
-      <c r="C37" s="81"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="G37" s="62"/>
-      <c r="H37" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="I37" s="60" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A38" s="103"/>
-      <c r="B38" s="79"/>
-      <c r="C38" s="82"/>
-      <c r="D38" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="F38" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="G38" s="71"/>
-      <c r="H38" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="I38" s="86"/>
-    </row>
-    <row r="39" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="103"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="G39" s="63"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="61"/>
-    </row>
-    <row r="40" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="103"/>
-      <c r="B40" s="33">
-        <v>20</v>
-      </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="I40" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A41" s="92"/>
-      <c r="B41" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="77"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="98"/>
-    </row>
-    <row r="42" spans="1:9" s="16" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="92"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="17">
-        <f>COUNTIF(C4:C40, "&lt;&gt;")</f>
-        <v>21</v>
-      </c>
-      <c r="D42" s="17">
-        <f>COUNTIF(D4:D40, "&lt;&gt;")</f>
-        <v>20</v>
-      </c>
-      <c r="E42" s="17">
-        <f t="shared" ref="E42:I42" si="0">COUNTIF(E4:E40, "&lt;&gt;")</f>
-        <v>9</v>
-      </c>
-      <c r="F42" s="17">
+      <c r="F41" s="15">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G42" s="17">
+      <c r="G41" s="15">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="H42" s="17">
+      <c r="H41" s="15">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="I42" s="17">
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="92"/>
-      <c r="B43" s="77" t="str">
-        <f>SUM(C42:I42) &amp; " Total Races (Prior to Breeders' Cup Weekend)"</f>
+    <row r="42" spans="1:9" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="117"/>
+      <c r="B42" s="99" t="str">
+        <f>SUM(C41:I41) &amp; " Total Races (Prior to Breeders' Cup Weekend)"</f>
         <v>95 Total Races (Prior to Breeders' Cup Weekend)</v>
       </c>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="77"/>
-    </row>
-    <row r="44" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="92"/>
-      <c r="B44" s="93" t="s">
+      <c r="C42" s="99"/>
+      <c r="D42" s="99"/>
+      <c r="E42" s="99"/>
+      <c r="F42" s="99"/>
+      <c r="G42" s="99"/>
+      <c r="H42" s="99"/>
+      <c r="I42" s="99"/>
+    </row>
+    <row r="43" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="117"/>
+      <c r="B43" s="124" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="93"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="94"/>
-      <c r="F44" s="95" t="s">
+      <c r="C43" s="124"/>
+      <c r="D43" s="124"/>
+      <c r="E43" s="125"/>
+      <c r="F43" s="126" t="s">
         <v>86</v>
       </c>
-      <c r="G44" s="96"/>
-      <c r="H44" s="96"/>
-      <c r="I44" s="97"/>
+      <c r="G43" s="127"/>
+      <c r="H43" s="127"/>
+      <c r="I43" s="128"/>
     </row>
   </sheetData>
-  <mergeCells count="76">
-    <mergeCell ref="B9:B10"/>
+  <mergeCells count="83">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="F44:I44"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="E33:E36"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="G33:G36"/>
-    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="F43:I43"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G32:G35"/>
+    <mergeCell ref="B32:B35"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="F15:F17"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="A2:A40"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="E15:E17"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="A2:A39"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="D20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="F20:F21"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="G11:G13"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="H15:H17"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="G36:G38"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="I36:I38"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="H32:H35"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="G27:G28"/>
     <mergeCell ref="H27:H28"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="I37:I39"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="H33:H36"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="F31:F32"/>
     <mergeCell ref="I27:I28"/>
-    <mergeCell ref="I20:I21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="I24:I26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="D14:D15"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="H9:H10"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I20:I21"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="51" fitToHeight="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
